--- a/Data_clean/MCAS/Estados_US/Edos_USA_2022/DELAWARE_2022.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2022/DELAWARE_2022.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D415"/>
+  <dimension ref="A1:D409"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Total</t>
@@ -457,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Los Cabos</t>
@@ -470,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -501,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Carmen</t>
@@ -514,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Total</t>
@@ -534,7 +564,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amatenango de la Frontera</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C12">
@@ -545,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Angel Albino Corzo</t>
@@ -558,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Arriaga</t>
@@ -571,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Bella Vista</t>
@@ -584,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Cacahoatán</t>
@@ -597,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Chamula</t>
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Chenalhó</t>
@@ -623,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Chicomuselo</t>
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>El Porvenir</t>
@@ -649,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Escuintla</t>
@@ -662,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -675,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -688,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -701,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>La Grandeza</t>
@@ -714,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -727,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -740,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -753,9 +863,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Marqués de Comillas</t>
+          <t>Marqués De Comillas</t>
         </is>
       </c>
       <c r="C29">
@@ -766,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Mazatán</t>
@@ -779,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -792,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Ocosingo</t>
@@ -805,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Palenque</t>
@@ -818,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Suchiate</t>
@@ -831,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -844,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -857,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Tuxtla Gutiérrez</t>
@@ -870,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Tuzantán</t>
@@ -883,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Unión Juárez</t>
@@ -896,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Villa Comaltitlán</t>
@@ -909,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Zinacantán</t>
@@ -922,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Total</t>
@@ -953,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -966,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Total</t>
@@ -997,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -1010,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1025,7 +1225,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1041,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -1054,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1067,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1080,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -1093,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1106,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>La Magdalena Contreras</t>
@@ -1119,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1132,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Milpa Alta</t>
@@ -1145,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -1158,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1171,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Xochimilco</t>
@@ -1184,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1215,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Durango</t>
@@ -1228,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Gómez Palacio</t>
@@ -1241,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -1254,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Mapimí</t>
@@ -1267,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -1280,9 +1565,14 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>San Pedro del Gallo</t>
+          <t>San Pedro Del Gallo</t>
         </is>
       </c>
       <c r="C68">
@@ -1293,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1308,12 +1603,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Acambay de Ruíz Castañeda</t>
+          <t>Acambay De Ruíz Castañeda</t>
         </is>
       </c>
       <c r="C70">
@@ -1324,9 +1619,14 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Almoloya de Alquisiras</t>
+          <t>Almoloya De Alquisiras</t>
         </is>
       </c>
       <c r="C71">
@@ -1337,9 +1637,14 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Almoloya de Juárez</t>
+          <t>Almoloya De Juárez</t>
         </is>
       </c>
       <c r="C72">
@@ -1350,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Amanalco</t>
@@ -1363,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Amecameca</t>
@@ -1376,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Atlacomulco</t>
@@ -1389,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Atlautla</t>
@@ -1402,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Calimaya</t>
@@ -1415,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Chalco</t>
@@ -1428,9 +1763,14 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Chapa de Mota</t>
+          <t>Chapa De Mota</t>
         </is>
       </c>
       <c r="C79">
@@ -1441,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Chimalhuacán</t>
@@ -1454,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Coatepec Harinas</t>
@@ -1467,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Cocotitlán</t>
@@ -1480,9 +1835,14 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C83">
@@ -1493,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>El Oro</t>
@@ -1506,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Huixquilucan</t>
@@ -1519,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Ixtapaluca</t>
@@ -1532,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ixtapan de la Sal</t>
+          <t>Ixtapan De La Sal</t>
         </is>
       </c>
       <c r="C87">
@@ -1545,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Ixtlahuaca</t>
@@ -1558,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Jilotepec</t>
@@ -1571,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Jiquipilco</t>
@@ -1584,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Joquicingo</t>
@@ -1597,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>La Paz</t>
@@ -1610,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Morelos</t>
@@ -1623,9 +2033,14 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C94">
@@ -1636,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -1649,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Ocuilan</t>
@@ -1662,9 +2087,14 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C97">
@@ -1675,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>San Mateo Atenco</t>
@@ -1688,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Santo Tomás</t>
@@ -1701,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Sultepec</t>
@@ -1714,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Tecámac</t>
@@ -1727,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -1740,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Temascaltepec</t>
@@ -1753,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -1766,9 +2231,14 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Tenango del Valle</t>
+          <t>Tenango Del Valle</t>
         </is>
       </c>
       <c r="C105">
@@ -1779,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Texcaltitlán</t>
@@ -1792,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Texcoco</t>
@@ -1805,9 +2285,14 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C108">
@@ -1818,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -1831,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -1844,9 +2339,14 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Valle de Chalco Solidaridad</t>
+          <t>Valle De Chalco Solidaridad</t>
         </is>
       </c>
       <c r="C111">
@@ -1857,9 +2357,14 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Villa de Allende</t>
+          <t>Villa De Allende</t>
         </is>
       </c>
       <c r="C112">
@@ -1870,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Villa Guerrero</t>
@@ -1883,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Zacualpan</t>
@@ -1896,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Zinacantepec</t>
@@ -1909,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Zumpahuacán</t>
@@ -1922,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1953,9 +2483,14 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Apaseo el Grande</t>
+          <t>Apaseo El Grande</t>
         </is>
       </c>
       <c r="C119">
@@ -1966,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -1979,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -1992,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Jerécuaro</t>
@@ -2005,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>León</t>
@@ -2018,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Moroleón</t>
@@ -2031,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -2044,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -2057,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>San Felipe</t>
@@ -2070,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Uriangato</t>
@@ -2083,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -2096,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2116,7 +2706,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C131">
@@ -2127,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Apaxtla</t>
@@ -2140,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Atlixtac</t>
@@ -2153,9 +2753,14 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C134">
@@ -2166,9 +2771,14 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C135">
@@ -2179,9 +2789,14 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Coahuayutla de José María Izazaga</t>
+          <t>Coahuayutla De José María Izazaga</t>
         </is>
       </c>
       <c r="C136">
@@ -2192,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Cocula</t>
@@ -2205,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Copalillo</t>
@@ -2218,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Copanatoyac</t>
@@ -2231,9 +2861,14 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C140">
@@ -2244,9 +2879,14 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Coyuca de Catalán</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C141">
@@ -2257,9 +2897,14 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Cuetzala del Progreso</t>
+          <t>Cuetzala Del Progreso</t>
         </is>
       </c>
       <c r="C142">
@@ -2270,9 +2915,14 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Cutzamala de Pinzón</t>
+          <t>Cutzamala De Pinzón</t>
         </is>
       </c>
       <c r="C143">
@@ -2283,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Eduardo Neri</t>
@@ -2296,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Florencio Villarreal</t>
@@ -2309,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>General Canuto A. Neri</t>
@@ -2322,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>General Heliodoro Castillo</t>
@@ -2335,9 +3005,14 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Huitzuco de los Figueroa</t>
+          <t>Huitzuco De Los Figueroa</t>
         </is>
       </c>
       <c r="C148">
@@ -2348,9 +3023,14 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Iguala de la Independencia</t>
+          <t>Iguala De La Independencia</t>
         </is>
       </c>
       <c r="C149">
@@ -2361,9 +3041,14 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>La Unión de Isidoro Montes de Oca</t>
+          <t>La Unión De Isidoro Montes De Oca</t>
         </is>
       </c>
       <c r="C150">
@@ -2374,6 +3059,11 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Leonardo Bravo</t>
@@ -2387,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Olinalá</t>
@@ -2400,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Pedro Ascencio Alquisiras</t>
@@ -2413,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -2426,6 +3131,11 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>San Miguel Totolapan</t>
@@ -2439,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Tecoanapa</t>
@@ -2452,9 +3167,14 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C157">
@@ -2465,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Teloloapan</t>
@@ -2478,9 +3203,14 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Tepecoacuilco de Trujano</t>
+          <t>Tepecoacuilco De Trujano</t>
         </is>
       </c>
       <c r="C159">
@@ -2491,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Tetipac</t>
@@ -2504,9 +3239,14 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Tixtla de Guerrero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C161">
@@ -2517,6 +3257,11 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>Tlacoachistlahuaca</t>
@@ -2530,9 +3275,14 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C163">
@@ -2543,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Xochistlahuaca</t>
@@ -2556,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2576,7 +3336,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Atotonilco el Grande</t>
+          <t>Atotonilco El Grande</t>
         </is>
       </c>
       <c r="C166">
@@ -2587,9 +3347,14 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Cuautepec de Hinojosa</t>
+          <t>Cuautepec De Hinojosa</t>
         </is>
       </c>
       <c r="C167">
@@ -2600,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Huehuetla</t>
@@ -2613,6 +3383,11 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -2626,9 +3401,14 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Jacala de Ledezma</t>
+          <t>Jacala De Ledezma</t>
         </is>
       </c>
       <c r="C170">
@@ -2639,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Metepec</t>
@@ -2652,9 +3437,14 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C172">
@@ -2665,6 +3455,11 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>San Felipe Orizatlán</t>
@@ -2678,6 +3473,11 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Tecozautla</t>
@@ -2691,9 +3491,14 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Tepehuacán de Guerrero</t>
+          <t>Tepehuacán De Guerrero</t>
         </is>
       </c>
       <c r="C175">
@@ -2704,9 +3509,14 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Tula de Allende</t>
+          <t>Tula De Allende</t>
         </is>
       </c>
       <c r="C176">
@@ -2717,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -2730,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2750,7 +3570,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Atemajac de Brizuela</t>
+          <t>Atemajac De Brizuela</t>
         </is>
       </c>
       <c r="C179">
@@ -2761,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>El Salto</t>
@@ -2774,9 +3599,14 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Encarnación de Díaz</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C181">
@@ -2787,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -2800,9 +3635,14 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C183">
@@ -2813,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Quitupan</t>
@@ -2826,9 +3671,14 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>San Martín de Bolaños</t>
+          <t>San Martín De Bolaños</t>
         </is>
       </c>
       <c r="C185">
@@ -2839,9 +3689,14 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>San Miguel el Alto</t>
+          <t>San Miguel El Alto</t>
         </is>
       </c>
       <c r="C186">
@@ -2852,9 +3707,14 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Tamazula de Gordiano</t>
+          <t>Tamazula De Gordiano</t>
         </is>
       </c>
       <c r="C187">
@@ -2865,6 +3725,11 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>Tlaquepaque</t>
@@ -2878,6 +3743,11 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -2891,9 +3761,14 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Zapotlán el Grande</t>
+          <t>Zapotlán El Grande</t>
         </is>
       </c>
       <c r="C190">
@@ -2904,6 +3779,11 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>Zapotlanejo</t>
@@ -2917,6 +3797,11 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2948,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Álvaro Obregón</t>
@@ -2961,6 +3851,11 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>Apatzingán</t>
@@ -2974,6 +3869,11 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>Carácuaro</t>
@@ -2987,6 +3887,11 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Coeneo</t>
@@ -3000,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Cuitzeo</t>
@@ -3013,6 +3923,11 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>Erongarícuaro</t>
@@ -3026,6 +3941,11 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -3039,6 +3959,11 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>Huandacareo</t>
@@ -3052,6 +3977,11 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>La Huacana</t>
@@ -3065,6 +3995,11 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -3078,6 +4013,11 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -3091,6 +4031,11 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -3104,6 +4049,11 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>Morelos</t>
@@ -3117,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Múgica</t>
@@ -3130,6 +4085,11 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>Nocupétaro</t>
@@ -3143,6 +4103,11 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -3156,6 +4121,11 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>Panindícuaro</t>
@@ -3169,6 +4139,11 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>Sahuayo</t>
@@ -3182,6 +4157,11 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>San Lucas</t>
@@ -3195,6 +4175,11 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>Tangamandapio</t>
@@ -3208,6 +4193,11 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Taretan</t>
@@ -3221,6 +4211,11 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>Tarímbaro</t>
@@ -3234,6 +4229,11 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>Tuzantla</t>
@@ -3247,6 +4247,11 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -3260,6 +4265,11 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -3273,6 +4283,11 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -3286,6 +4301,11 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3317,6 +4337,11 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Axochiapan</t>
@@ -3330,6 +4355,11 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
           <t>Ayala</t>
@@ -3343,6 +4373,11 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -3356,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -3369,6 +4409,11 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>Jojutla</t>
@@ -3382,9 +4427,14 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Puente de Ixtla</t>
+          <t>Puente De Ixtla</t>
         </is>
       </c>
       <c r="C227">
@@ -3395,6 +4445,11 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>Temixco</t>
@@ -3408,6 +4463,11 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>Tepalcingo</t>
@@ -3421,6 +4481,11 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>Tetecala</t>
@@ -3434,9 +4499,14 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Tetela del Volcán</t>
+          <t>Tetela Del Volcán</t>
         </is>
       </c>
       <c r="C231">
@@ -3447,9 +4517,14 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Tlaltizapán de Zapata</t>
+          <t>Tlaltizapán De Zapata</t>
         </is>
       </c>
       <c r="C232">
@@ -3460,6 +4535,11 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
           <t>Tlaquiltenango</t>
@@ -3473,6 +4553,11 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>Tlayacapan</t>
@@ -3486,6 +4571,11 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>Xochitepec</t>
@@ -3499,6 +4589,11 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>Yautepec</t>
@@ -3512,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>Zacatepec</t>
@@ -3525,6 +4625,11 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3545,7 +4650,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Amatlán de Cañas</t>
+          <t>Amatlán De Cañas</t>
         </is>
       </c>
       <c r="C239">
@@ -3556,6 +4661,11 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>Compostela</t>
@@ -3569,6 +4679,11 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>Santiago Ixcuintla</t>
@@ -3582,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3613,6 +4733,11 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3633,7 +4758,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Acatlán de Pérez Figueroa</t>
+          <t>Acatlán De Pérez Figueroa</t>
         </is>
       </c>
       <c r="C245">
@@ -3644,6 +4769,11 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>Candelaria Loxicha</t>
@@ -3657,6 +4787,11 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>Cosolapa</t>
@@ -3670,9 +4805,14 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Huautla de Jiménez</t>
+          <t>Huautla De Jiménez</t>
         </is>
       </c>
       <c r="C248">
@@ -3683,9 +4823,14 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Mariscala de Juárez</t>
+          <t>Mariscala De Juárez</t>
         </is>
       </c>
       <c r="C249">
@@ -3696,6 +4841,11 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>Matías Romero Avendaño</t>
@@ -3709,9 +4859,14 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Nejapa de Madero</t>
+          <t>Nejapa De Madero</t>
         </is>
       </c>
       <c r="C251">
@@ -3722,9 +4877,14 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C252">
@@ -3735,6 +4895,11 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>San Agustín Etla</t>
@@ -3748,6 +4913,11 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>San Andrés Yaá</t>
@@ -3761,9 +4931,14 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>San Felipe Jalapa de Díaz</t>
+          <t>San Felipe Jalapa De Díaz</t>
         </is>
       </c>
       <c r="C255">
@@ -3774,6 +4949,11 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -3787,6 +4967,11 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>San Juan Cacahuatepec</t>
@@ -3800,6 +4985,11 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>San Miguel Aloápam</t>
@@ -3813,6 +5003,11 @@
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
           <t>San Pablo Huitzo</t>
@@ -3826,6 +5021,11 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
           <t>San Pedro Tapanatepec</t>
@@ -3839,6 +5039,11 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>San Pedro Yaneri</t>
@@ -3852,6 +5057,11 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>San Sebastián Abasolo</t>
@@ -3865,6 +5075,11 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
           <t>Santa María Chimalapa</t>
@@ -3878,6 +5093,11 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>Santa María Jacatepec</t>
@@ -3891,6 +5111,11 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>Santiago Ixtayutla</t>
@@ -3904,6 +5129,11 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>Santiago Jamiltepec</t>
@@ -3917,6 +5147,11 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -3930,6 +5165,11 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
           <t>Santiago Tamazola</t>
@@ -3943,6 +5183,11 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
           <t>Santo Domingo Tepuxtepec</t>
@@ -3956,6 +5201,11 @@
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
           <t>Santos Reyes Nopala</t>
@@ -3969,9 +5219,14 @@
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Zimatlán de Álvarez</t>
+          <t>Zimatlán De Álvarez</t>
         </is>
       </c>
       <c r="C271">
@@ -3982,6 +5237,11 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4013,6 +5273,11 @@
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
           <t>Ajalpan</t>
@@ -4026,6 +5291,11 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
           <t>Atexcal</t>
@@ -4039,6 +5309,11 @@
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -4052,6 +5327,11 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
           <t>Atzala</t>
@@ -4065,6 +5345,11 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
           <t>Calpan</t>
@@ -4078,6 +5363,11 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>Chiautla</t>
@@ -4091,6 +5381,11 @@
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
           <t>Chiautzingo</t>
@@ -4104,6 +5399,11 @@
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
           <t>Chichiquila</t>
@@ -4117,6 +5417,11 @@
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
           <t>Chietla</t>
@@ -4130,6 +5435,11 @@
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
           <t>Domingo Arenas</t>
@@ -4143,6 +5453,11 @@
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
           <t>Epatlán</t>
@@ -4156,6 +5471,11 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -4169,6 +5489,11 @@
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
           <t>Hermenegildo Galeana</t>
@@ -4182,9 +5507,14 @@
       </c>
     </row>
     <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Huehuetlán el Chico</t>
+          <t>Huehuetlán El Chico</t>
         </is>
       </c>
       <c r="C287">
@@ -4195,6 +5525,11 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
           <t>Huejotzingo</t>
@@ -4208,6 +5543,11 @@
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
           <t>Huitziltepec</t>
@@ -4221,6 +5561,11 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
           <t>Ixtacamaxtitlán</t>
@@ -4234,9 +5579,14 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C291">
@@ -4247,6 +5597,11 @@
       </c>
     </row>
     <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
           <t>Juan C. Bonilla</t>
@@ -4260,6 +5615,11 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
           <t>Libres</t>
@@ -4273,9 +5633,14 @@
       </c>
     </row>
     <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Palmar de Bravo</t>
+          <t>Palmar De Bravo</t>
         </is>
       </c>
       <c r="C294">
@@ -4286,6 +5651,11 @@
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -4299,6 +5669,11 @@
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
           <t>Quecholac</t>
@@ -4312,6 +5687,11 @@
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
           <t>San José Miahuatlán</t>
@@ -4325,6 +5705,11 @@
       </c>
     </row>
     <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
           <t>San Martín Texmelucan</t>
@@ -4338,6 +5723,11 @@
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
           <t>San Pablo Anicano</t>
@@ -4351,6 +5741,11 @@
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -4364,6 +5759,11 @@
       </c>
     </row>
     <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
           <t>San Pedro Yeloixtlahuaca</t>
@@ -4377,9 +5777,14 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Tecali de Herrera</t>
+          <t>Tecali De Herrera</t>
         </is>
       </c>
       <c r="C302">
@@ -4390,6 +5795,11 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
           <t>Tecamachalco</t>
@@ -4403,6 +5813,11 @@
       </c>
     </row>
     <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -4416,6 +5831,11 @@
       </c>
     </row>
     <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
           <t>Tehuitzingo</t>
@@ -4429,6 +5849,11 @@
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
           <t>Teopantlán</t>
@@ -4442,9 +5867,14 @@
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Tepanco de López</t>
+          <t>Tepanco De López</t>
         </is>
       </c>
       <c r="C307">
@@ -4455,9 +5885,14 @@
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Tepatlaxco de Hidalgo</t>
+          <t>Tepatlaxco De Hidalgo</t>
         </is>
       </c>
       <c r="C308">
@@ -4468,6 +5903,11 @@
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -4481,6 +5921,11 @@
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
           <t>Tepeyahualco</t>
@@ -4494,9 +5939,14 @@
       </c>
     </row>
     <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Tetela de Ocampo</t>
+          <t>Tetela De Ocampo</t>
         </is>
       </c>
       <c r="C311">
@@ -4507,6 +5957,11 @@
       </c>
     </row>
     <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B312" t="inlineStr">
         <is>
           <t>Teziutlán</t>
@@ -4520,9 +5975,14 @@
       </c>
     </row>
     <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C313">
@@ -4533,6 +5993,11 @@
       </c>
     </row>
     <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
           <t>Tlahuapan</t>
@@ -4546,6 +6011,11 @@
       </c>
     </row>
     <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr">
         <is>
           <t>Tlaltenango</t>
@@ -4559,6 +6029,11 @@
       </c>
     </row>
     <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
           <t>Tlatlauquitepec</t>
@@ -4572,6 +6047,11 @@
       </c>
     </row>
     <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B317" t="inlineStr">
         <is>
           <t>Tlaxco</t>
@@ -4585,6 +6065,11 @@
       </c>
     </row>
     <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
           <t>Tochtepec</t>
@@ -4598,6 +6083,11 @@
       </c>
     </row>
     <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -4611,6 +6101,11 @@
       </c>
     </row>
     <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -4624,6 +6119,11 @@
       </c>
     </row>
     <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
           <t>Xicotepec</t>
@@ -4637,6 +6137,11 @@
       </c>
     </row>
     <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
           <t>Xiutetelco</t>
@@ -4650,6 +6155,11 @@
       </c>
     </row>
     <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr">
         <is>
           <t>Zacapala</t>
@@ -4663,6 +6173,11 @@
       </c>
     </row>
     <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr">
         <is>
           <t>Zacapoaxtla</t>
@@ -4676,6 +6191,11 @@
       </c>
     </row>
     <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr">
         <is>
           <t>Zapotitlán</t>
@@ -4689,6 +6209,11 @@
       </c>
     </row>
     <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B326" t="inlineStr">
         <is>
           <t>Zautla</t>
@@ -4702,6 +6227,11 @@
       </c>
     </row>
     <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B327" t="inlineStr">
         <is>
           <t>Zoquitlán</t>
@@ -4715,6 +6245,11 @@
       </c>
     </row>
     <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B328" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4735,7 +6270,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C329">
@@ -4746,6 +6281,11 @@
       </c>
     </row>
     <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
           <t>Colón</t>
@@ -4759,6 +6299,11 @@
       </c>
     </row>
     <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B331" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -4772,6 +6317,11 @@
       </c>
     </row>
     <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B332" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4792,7 +6342,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Ciudad del Maíz</t>
+          <t>Ciudad Del Maíz</t>
         </is>
       </c>
       <c r="C333">
@@ -4803,6 +6353,11 @@
       </c>
     </row>
     <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B334" t="inlineStr">
         <is>
           <t>Ciudad Valles</t>
@@ -4816,6 +6371,11 @@
       </c>
     </row>
     <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr">
         <is>
           <t>Rayón</t>
@@ -4829,6 +6389,11 @@
       </c>
     </row>
     <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B336" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -4842,6 +6407,11 @@
       </c>
     </row>
     <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B337" t="inlineStr">
         <is>
           <t>Salinas</t>
@@ -4855,9 +6425,14 @@
       </c>
     </row>
     <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>San Ciro de Acosta</t>
+          <t>San Ciro De Acosta</t>
         </is>
       </c>
       <c r="C338">
@@ -4868,6 +6443,11 @@
       </c>
     </row>
     <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B339" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -4881,6 +6461,11 @@
       </c>
     </row>
     <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B340" t="inlineStr">
         <is>
           <t>Tamasopo</t>
@@ -4894,6 +6479,11 @@
       </c>
     </row>
     <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr">
         <is>
           <t>Tamazunchale</t>
@@ -4907,9 +6497,14 @@
       </c>
     </row>
     <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Villa de Arista</t>
+          <t>Villa De Arista</t>
         </is>
       </c>
       <c r="C342">
@@ -4920,6 +6515,11 @@
       </c>
     </row>
     <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B343" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4951,6 +6551,11 @@
       </c>
     </row>
     <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B345" t="inlineStr">
         <is>
           <t>Navolato</t>
@@ -4964,6 +6569,11 @@
       </c>
     </row>
     <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B346" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4995,6 +6605,11 @@
       </c>
     </row>
     <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B348" t="inlineStr">
         <is>
           <t>Macuspana</t>
@@ -5008,6 +6623,11 @@
       </c>
     </row>
     <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B349" t="inlineStr">
         <is>
           <t>Paraíso</t>
@@ -5021,6 +6641,11 @@
       </c>
     </row>
     <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B350" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5052,6 +6677,11 @@
       </c>
     </row>
     <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B352" t="inlineStr">
         <is>
           <t>El Mante</t>
@@ -5065,6 +6695,11 @@
       </c>
     </row>
     <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B353" t="inlineStr">
         <is>
           <t>González</t>
@@ -5078,6 +6713,11 @@
       </c>
     </row>
     <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B354" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -5091,6 +6731,11 @@
       </c>
     </row>
     <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B355" t="inlineStr">
         <is>
           <t>Río Bravo</t>
@@ -5104,6 +6749,11 @@
       </c>
     </row>
     <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B356" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5135,6 +6785,11 @@
       </c>
     </row>
     <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B358" t="inlineStr">
         <is>
           <t>Huamantla</t>
@@ -5148,6 +6803,11 @@
       </c>
     </row>
     <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B359" t="inlineStr">
         <is>
           <t>Hueyotlipan</t>
@@ -5161,6 +6821,11 @@
       </c>
     </row>
     <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B360" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -5174,6 +6839,11 @@
       </c>
     </row>
     <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B361" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5205,9 +6875,14 @@
       </c>
     </row>
     <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Amatlán de los Reyes</t>
+          <t>Amatlán De Los Reyes</t>
         </is>
       </c>
       <c r="C363">
@@ -5218,6 +6893,11 @@
       </c>
     </row>
     <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B364" t="inlineStr">
         <is>
           <t>Angel R. Cabada</t>
@@ -5231,6 +6911,11 @@
       </c>
     </row>
     <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B365" t="inlineStr">
         <is>
           <t>Apazapan</t>
@@ -5244,6 +6929,11 @@
       </c>
     </row>
     <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B366" t="inlineStr">
         <is>
           <t>Atlahuilco</t>
@@ -5257,6 +6947,11 @@
       </c>
     </row>
     <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B367" t="inlineStr">
         <is>
           <t>Atzalan</t>
@@ -5270,9 +6965,14 @@
       </c>
     </row>
     <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Castillo de Teayo</t>
+          <t>Castillo De Teayo</t>
         </is>
       </c>
       <c r="C368">
@@ -5283,6 +6983,11 @@
       </c>
     </row>
     <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B369" t="inlineStr">
         <is>
           <t>Catemaco</t>
@@ -5296,6 +7001,11 @@
       </c>
     </row>
     <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B370" t="inlineStr">
         <is>
           <t>Cazones</t>
@@ -5309,6 +7019,11 @@
       </c>
     </row>
     <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B371" t="inlineStr">
         <is>
           <t>Chacaltianguis</t>
@@ -5322,6 +7037,11 @@
       </c>
     </row>
     <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B372" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -5335,9 +7055,14 @@
       </c>
     </row>
     <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Cosamaloapan de Carpio</t>
+          <t>Cosamaloapan De Carpio</t>
         </is>
       </c>
       <c r="C373">
@@ -5348,6 +7073,11 @@
       </c>
     </row>
     <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B374" t="inlineStr">
         <is>
           <t>Cuitláhuac</t>
@@ -5361,9 +7091,14 @@
       </c>
     </row>
     <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C375">
@@ -5374,6 +7109,11 @@
       </c>
     </row>
     <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B376" t="inlineStr">
         <is>
           <t>Jáltipan</t>
@@ -5387,6 +7127,11 @@
       </c>
     </row>
     <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B377" t="inlineStr">
         <is>
           <t>Jesús Carranza</t>
@@ -5400,9 +7145,14 @@
       </c>
     </row>
     <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Lerdo de Tejada</t>
+          <t>Lerdo De Tejada</t>
         </is>
       </c>
       <c r="C378">
@@ -5413,9 +7163,14 @@
       </c>
     </row>
     <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C379">
@@ -5426,6 +7181,11 @@
       </c>
     </row>
     <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B380" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -5439,6 +7199,11 @@
       </c>
     </row>
     <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B381" t="inlineStr">
         <is>
           <t>Naolinco</t>
@@ -5452,6 +7217,11 @@
       </c>
     </row>
     <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B382" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -5465,6 +7235,11 @@
       </c>
     </row>
     <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B383" t="inlineStr">
         <is>
           <t>Pánuco</t>
@@ -5478,6 +7253,11 @@
       </c>
     </row>
     <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B384" t="inlineStr">
         <is>
           <t>Papantla</t>
@@ -5491,9 +7271,14 @@
       </c>
     </row>
     <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Paso de Ovejas</t>
+          <t>Paso De Ovejas</t>
         </is>
       </c>
       <c r="C385">
@@ -5504,6 +7289,11 @@
       </c>
     </row>
     <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B386" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -5517,6 +7307,11 @@
       </c>
     </row>
     <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B387" t="inlineStr">
         <is>
           <t>San Juan Evangelista</t>
@@ -5530,9 +7325,14 @@
       </c>
     </row>
     <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Sayula de Alemán</t>
+          <t>Sayula De Alemán</t>
         </is>
       </c>
       <c r="C388">
@@ -5543,6 +7343,11 @@
       </c>
     </row>
     <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B389" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -5556,6 +7361,11 @@
       </c>
     </row>
     <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B390" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -5569,6 +7379,11 @@
       </c>
     </row>
     <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B391" t="inlineStr">
         <is>
           <t>Tres Valles</t>
@@ -5582,6 +7397,11 @@
       </c>
     </row>
     <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B392" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -5595,6 +7415,11 @@
       </c>
     </row>
     <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B393" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -5608,6 +7433,11 @@
       </c>
     </row>
     <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B394" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -5621,6 +7451,11 @@
       </c>
     </row>
     <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B395" t="inlineStr">
         <is>
           <t>Zentla</t>
@@ -5634,6 +7469,11 @@
       </c>
     </row>
     <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B396" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5665,6 +7505,11 @@
       </c>
     </row>
     <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B398" t="inlineStr">
         <is>
           <t>Teya</t>
@@ -5678,6 +7523,11 @@
       </c>
     </row>
     <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B399" t="inlineStr">
         <is>
           <t>Tizimín</t>
@@ -5691,6 +7541,11 @@
       </c>
     </row>
     <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B400" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5722,6 +7577,11 @@
       </c>
     </row>
     <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B402" t="inlineStr">
         <is>
           <t>Pinos</t>
@@ -5735,6 +7595,11 @@
       </c>
     </row>
     <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B403" t="inlineStr">
         <is>
           <t>Río Grande</t>
@@ -5748,6 +7613,11 @@
       </c>
     </row>
     <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B404" t="inlineStr">
         <is>
           <t>Sain Alto</t>
@@ -5761,6 +7631,11 @@
       </c>
     </row>
     <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B405" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -5774,9 +7649,14 @@
       </c>
     </row>
     <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Villa de Cos</t>
+          <t>Villa De Cos</t>
         </is>
       </c>
       <c r="C406">
@@ -5787,6 +7667,11 @@
       </c>
     </row>
     <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B407" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -5800,6 +7685,11 @@
       </c>
     </row>
     <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B408" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5823,41 +7713,6 @@
       </c>
       <c r="D409">
         <v>1</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 566,547</t>
-        </is>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>Mayo de 2023</t>
-        </is>
       </c>
     </row>
   </sheetData>
